--- a/evaluation_surveys/027_surgical_precision_evaluation_survey--evaluation_surveys.xlsx
+++ b/evaluation_surveys/027_surgical_precision_evaluation_survey--evaluation_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_rated',_'value':_'not_rated'}</t>
+          <t>not_rated</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not rated', 'value': 'Not rated'}</t>
+          <t>Not rated</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'satisfactory',_'value':_'satisfactory'}</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Satisfactory', 'value': 'Satisfactory'}</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unsatisfactory',_'value':_'unsatisfactory'}</t>
+          <t>unsatisfactory</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unsatisfactory', 'value': 'Unsatisfactory'}</t>
+          <t>Unsatisfactory</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_assessed',_'value':_'not_assessed'}</t>
+          <t>not_assessed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not assessed', 'value': 'Not assessed'}</t>
+          <t>Not assessed</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'simple',_'value':_'simple'}</t>
+          <t>simple</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Simple', 'value': 'Simple'}</t>
+          <t>Simple</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'complex',_'value':_'complex'}</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Complex', 'value': 'Complex'}</t>
+          <t>Complex</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_30_minutes',_'value':_'less_than_30_minutes'}</t>
+          <t>less_than_30_minutes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 30 minutes', 'value': 'Less than 30 minutes'}</t>
+          <t>Less than 30 minutes</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'30-60_minutes',_'value':_'30-60_minutes'}</t>
+          <t>30-60_minutes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '30-60 minutes', 'value': '30-60 minutes'}</t>
+          <t>30-60 minutes</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'more_than_1_hour',_'value':_'more_than_1_hour'}</t>
+          <t>more_than_1_hour</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'More than 1 hour', 'value': 'More than 1 hour'}</t>
+          <t>More than 1 hour</t>
         </is>
       </c>
     </row>
